--- a/问题三/results/表3_指定日期紧急购电量.xlsx
+++ b/问题三/results/表3_指定日期紧急购电量.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -506,176 +506,20 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>7:00-10:00</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>2332.340137499996</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>4:00-4:50</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>5.241599999999949</v>
-      </c>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>6:30-6:50</t>
+          <t>20:20-20:30</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>106.0138903333358</v>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>7:10-11:50</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>2465.557035333339</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>11:10-11:20</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>229.3781333333345</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>5:00-5:50</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>362.6616</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>7:00-9:50</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>2114.313433333334</v>
-      </c>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>11:30-12:00</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>291.0217000000002</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>6:00-7:20</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>713.1668166666661</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>10:00-12:00</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>974.1067333333342</v>
-      </c>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>12:40-13:00</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>85.1568666666667</v>
-      </c>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>13:50-14:00</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>14.52828333333332</v>
-      </c>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>13:20-14:00</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>115.6718500000006</v>
-      </c>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n"/>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>15:50-16:00</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>6.975883333333286</v>
-      </c>
-      <c r="H7" s="1" t="n"/>
-      <c r="I7" s="1" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>15:50-16:00</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>16.78683333333311</v>
-      </c>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
-      <c r="I8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>16:50-17:00</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>2.985850000000028</v>
-      </c>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
+        <v>6.375</v>
+      </c>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/问题三/results/表3_指定日期紧急购电量.xlsx
+++ b/问题三/results/表3_指定日期紧急购电量.xlsx
@@ -506,8 +506,14 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>9:00-10:00</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>407.8953815000039</v>
+      </c>
       <c r="D3" s="1" t="n"/>
       <c r="E3" s="1" t="n"/>
       <c r="F3" s="1" t="inlineStr">
